--- a/excel_files/MusicBrainz_Picard_Tag_Map.xlsx
+++ b/excel_files/MusicBrainz_Picard_Tag_Map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3B58A2-7161-4D00-85D4-E0B888B15937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5768753-AD59-44FC-BDFE-812F44E4F41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28785" yWindow="15975" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="449">
   <si>
     <t>Tag Name</t>
   </si>
@@ -1379,6 +1379,12 @@
   </si>
   <si>
     <t>TXXX:Writer (Picard&gt;=1.3)</t>
+  </si>
+  <si>
+    <t>Vorbis (flac)</t>
+  </si>
+  <si>
+    <t>Vorbis datatype</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" customWidth="1"/>
@@ -1816,11 +1822,12 @@
     <col min="5" max="5" width="54.28515625" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
     <col min="7" max="7" width="33.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="255.7109375" customWidth="1"/>
+    <col min="8" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1846,10 +1853,16 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1868,11 +1881,13 @@
         <v>13</v>
       </c>
       <c r="H2" s="4"/>
-      <c r="I2" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1891,11 +1906,13 @@
         <v>19</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="I3" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
@@ -1920,11 +1937,13 @@
       <c r="H4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>28</v>
       </c>
@@ -1949,11 +1968,13 @@
       <c r="H5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -1972,11 +1993,13 @@
         <v>38</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" t="s">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -1995,11 +2018,13 @@
         <v>44</v>
       </c>
       <c r="H7" s="4"/>
-      <c r="I7" t="s">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -2018,11 +2043,13 @@
         <v>49</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" t="s">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>51</v>
       </c>
@@ -2047,11 +2074,13 @@
       <c r="H9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
@@ -2070,11 +2099,13 @@
         <v>61</v>
       </c>
       <c r="H10" s="4"/>
-      <c r="I10" t="s">
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -2093,8 +2124,10 @@
         <v>67</v>
       </c>
       <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>68</v>
       </c>
@@ -2113,8 +2146,10 @@
         <v>68</v>
       </c>
       <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
@@ -2133,8 +2168,10 @@
         <v>76</v>
       </c>
       <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>77</v>
       </c>
@@ -2153,8 +2190,10 @@
         <v>81</v>
       </c>
       <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>82</v>
       </c>
@@ -2173,8 +2212,10 @@
         <v>86</v>
       </c>
       <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>87</v>
       </c>
@@ -2199,8 +2240,10 @@
       <c r="H16" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>92</v>
       </c>
@@ -2223,8 +2266,10 @@
       <c r="H17" s="12" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>98</v>
       </c>
@@ -2249,8 +2294,10 @@
       <c r="H18" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>103</v>
       </c>
@@ -2269,8 +2316,10 @@
         <v>107</v>
       </c>
       <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -2289,8 +2338,10 @@
         <v>112</v>
       </c>
       <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>113</v>
       </c>
@@ -2315,8 +2366,10 @@
       <c r="H21" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>118</v>
       </c>
@@ -2335,8 +2388,10 @@
         <v>122</v>
       </c>
       <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>123</v>
       </c>
@@ -2359,8 +2414,10 @@
       <c r="H23" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>129</v>
       </c>
@@ -2379,8 +2436,10 @@
         <v>133</v>
       </c>
       <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>134</v>
       </c>
@@ -2399,8 +2458,10 @@
         <v>138</v>
       </c>
       <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>139</v>
       </c>
@@ -2419,8 +2480,10 @@
         <v>142</v>
       </c>
       <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>143</v>
       </c>
@@ -2439,8 +2502,10 @@
         <v>147</v>
       </c>
       <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>148</v>
       </c>
@@ -2459,8 +2524,10 @@
         <v>49</v>
       </c>
       <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>151</v>
       </c>
@@ -2485,8 +2552,10 @@
       <c r="H29" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>156</v>
       </c>
@@ -2505,8 +2574,10 @@
         <v>160</v>
       </c>
       <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -2525,8 +2596,10 @@
         <v>165</v>
       </c>
       <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>166</v>
       </c>
@@ -2545,8 +2618,10 @@
         <v>170</v>
       </c>
       <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>171</v>
       </c>
@@ -2565,8 +2640,10 @@
         <v>175</v>
       </c>
       <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>176</v>
       </c>
@@ -2585,8 +2662,10 @@
         <v>49</v>
       </c>
       <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>180</v>
       </c>
@@ -2605,8 +2684,10 @@
         <v>184</v>
       </c>
       <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>185</v>
       </c>
@@ -2625,8 +2706,10 @@
         <v>189</v>
       </c>
       <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>190</v>
       </c>
@@ -2651,8 +2734,10 @@
       <c r="H37" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>196</v>
       </c>
@@ -2671,8 +2756,10 @@
         <v>200</v>
       </c>
       <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>201</v>
       </c>
@@ -2691,8 +2778,10 @@
         <v>205</v>
       </c>
       <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>206</v>
       </c>
@@ -2711,8 +2800,10 @@
         <v>210</v>
       </c>
       <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>211</v>
       </c>
@@ -2731,8 +2822,10 @@
         <v>49</v>
       </c>
       <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>215</v>
       </c>
@@ -2751,8 +2844,10 @@
         <v>49</v>
       </c>
       <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>219</v>
       </c>
@@ -2771,8 +2866,10 @@
         <v>49</v>
       </c>
       <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>222</v>
       </c>
@@ -2791,8 +2888,10 @@
         <v>226</v>
       </c>
       <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>227</v>
       </c>
@@ -2811,8 +2910,10 @@
         <v>231</v>
       </c>
       <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>232</v>
       </c>
@@ -2831,8 +2932,10 @@
         <v>236</v>
       </c>
       <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>237</v>
       </c>
@@ -2851,8 +2954,10 @@
         <v>241</v>
       </c>
       <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>242</v>
       </c>
@@ -2871,8 +2976,10 @@
         <v>246</v>
       </c>
       <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>247</v>
       </c>
@@ -2891,8 +2998,10 @@
         <v>251</v>
       </c>
       <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>252</v>
       </c>
@@ -2911,8 +3020,10 @@
         <v>256</v>
       </c>
       <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>257</v>
       </c>
@@ -2931,8 +3042,10 @@
         <v>261</v>
       </c>
       <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>262</v>
       </c>
@@ -2951,8 +3064,10 @@
         <v>266</v>
       </c>
       <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>267</v>
       </c>
@@ -2971,8 +3086,10 @@
         <v>271</v>
       </c>
       <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>272</v>
       </c>
@@ -2991,8 +3108,10 @@
         <v>276</v>
       </c>
       <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>277</v>
       </c>
@@ -3011,8 +3130,10 @@
         <v>49</v>
       </c>
       <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>281</v>
       </c>
@@ -3031,8 +3152,10 @@
         <v>285</v>
       </c>
       <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>286</v>
       </c>
@@ -3051,8 +3174,10 @@
         <v>289</v>
       </c>
       <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>290</v>
       </c>
@@ -3071,8 +3196,10 @@
         <v>293</v>
       </c>
       <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>294</v>
       </c>
@@ -3091,8 +3218,10 @@
         <v>297</v>
       </c>
       <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>298</v>
       </c>
@@ -3111,8 +3240,10 @@
         <v>301</v>
       </c>
       <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>302</v>
       </c>
@@ -3135,8 +3266,10 @@
       <c r="H61" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>307</v>
       </c>
@@ -3155,8 +3288,10 @@
         <v>49</v>
       </c>
       <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>310</v>
       </c>
@@ -3175,8 +3310,10 @@
         <v>49</v>
       </c>
       <c r="H63" s="4"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>313</v>
       </c>
@@ -3195,8 +3332,10 @@
         <v>49</v>
       </c>
       <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>316</v>
       </c>
@@ -3215,8 +3354,10 @@
         <v>320</v>
       </c>
       <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>321</v>
       </c>
@@ -3235,8 +3376,10 @@
         <v>324</v>
       </c>
       <c r="H66" s="4"/>
-    </row>
-    <row r="67" spans="1:9" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="1:11" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>325</v>
       </c>
@@ -3261,8 +3404,10 @@
       <c r="H67" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>330</v>
       </c>
@@ -3281,8 +3426,10 @@
         <v>334</v>
       </c>
       <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>335</v>
       </c>
@@ -3307,11 +3454,13 @@
       <c r="H69" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="7" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>342</v>
       </c>
@@ -3330,8 +3479,10 @@
         <v>346</v>
       </c>
       <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>347</v>
       </c>
@@ -3350,8 +3501,10 @@
         <v>351</v>
       </c>
       <c r="H71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>352</v>
       </c>
@@ -3370,8 +3523,10 @@
         <v>356</v>
       </c>
       <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+    </row>
+    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>357</v>
       </c>
@@ -3390,8 +3545,10 @@
         <v>361</v>
       </c>
       <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>362</v>
       </c>
@@ -3410,8 +3567,10 @@
         <v>366</v>
       </c>
       <c r="H74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>367</v>
       </c>
@@ -3430,8 +3589,10 @@
         <v>371</v>
       </c>
       <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>372</v>
       </c>
@@ -3450,8 +3611,10 @@
         <v>376</v>
       </c>
       <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>377</v>
       </c>
@@ -3470,8 +3633,10 @@
         <v>381</v>
       </c>
       <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>382</v>
       </c>
@@ -3490,8 +3655,10 @@
         <v>386</v>
       </c>
       <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>387</v>
       </c>
@@ -3510,8 +3677,10 @@
         <v>391</v>
       </c>
       <c r="H79" s="4"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>392</v>
       </c>
@@ -3530,8 +3699,10 @@
         <v>396</v>
       </c>
       <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>397</v>
       </c>
@@ -3550,8 +3721,10 @@
         <v>49</v>
       </c>
       <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>400</v>
       </c>
@@ -3570,8 +3743,10 @@
         <v>49</v>
       </c>
       <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>403</v>
       </c>
@@ -3590,8 +3765,10 @@
         <v>49</v>
       </c>
       <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>407</v>
       </c>
@@ -3610,8 +3787,10 @@
         <v>411</v>
       </c>
       <c r="H84" s="4"/>
-    </row>
-    <row r="85" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="1:10" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>412</v>
       </c>
@@ -3636,8 +3815,10 @@
       <c r="H85" s="9" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>417</v>
       </c>
@@ -3656,8 +3837,10 @@
         <v>49</v>
       </c>
       <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" spans="1:10" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>421</v>
       </c>
@@ -3682,8 +3865,10 @@
       <c r="H87" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I87" s="9"/>
+      <c r="J87" s="9"/>
+    </row>
+    <row r="88" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>425</v>
       </c>
@@ -3708,8 +3893,10 @@
       <c r="H88" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>430</v>
       </c>
@@ -3728,8 +3915,10 @@
         <v>434</v>
       </c>
       <c r="H89" s="4"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>435</v>
       </c>
@@ -3748,8 +3937,10 @@
         <v>438</v>
       </c>
       <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>439</v>
       </c>
@@ -3768,8 +3959,10 @@
         <v>443</v>
       </c>
       <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>444</v>
       </c>
@@ -3788,8 +3981,10 @@
         <v>49</v>
       </c>
       <c r="H92" s="4"/>
-    </row>
-    <row r="94" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+    </row>
+    <row r="94" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B94" s="18"/>
     </row>
   </sheetData>
